--- a/Indomie Clients Details/Clinix.xlsx
+++ b/Indomie Clients Details/Clinix.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C85F08-1BCE-4064-BB4A-EACD9F3C4CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2853647A-7B08-430D-90C9-17049A5D58D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3328,7 +3328,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -3356,7 +3356,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -4549,7 +4549,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -4577,7 +4577,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -5770,7 +5770,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -5798,7 +5798,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -6991,7 +6991,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -7019,7 +7019,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -8212,7 +8212,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -8240,7 +8240,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -9433,7 +9433,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -9461,7 +9461,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -10651,7 +10651,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -10679,7 +10679,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -11868,7 +11868,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -11896,7 +11896,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -13085,7 +13085,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -13113,7 +13113,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -14302,7 +14302,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -14330,7 +14330,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -18269,7 +18269,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -18297,7 +18297,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -19486,7 +19486,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -19514,7 +19514,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -20703,7 +20703,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -20731,7 +20731,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -21920,7 +21920,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -21948,7 +21948,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23142,7 +23142,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -23170,7 +23170,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -24508,7 +24508,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -24536,7 +24536,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -25716,7 +25716,7 @@
       <c r="L3" s="202"/>
       <c r="M3" s="202"/>
       <c r="N3" s="201">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="O3" s="201"/>
       <c r="P3" s="201"/>
@@ -25744,7 +25744,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -25772,7 +25772,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -26677,10 +26677,7 @@
       <c r="E26" s="145"/>
       <c r="F26" s="145"/>
       <c r="G26" s="146"/>
-      <c r="H26" s="146">
-        <f>H25/40</f>
-        <v>38</v>
-      </c>
+      <c r="H26" s="146"/>
       <c r="I26" s="147"/>
       <c r="K26" s="148"/>
       <c r="L26" s="148"/>
@@ -26945,7 +26942,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
@@ -27037,7 +27034,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -27065,7 +27062,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -28257,7 +28254,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -28285,7 +28282,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -29478,7 +29475,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -29506,7 +29503,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -30699,7 +30696,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -30727,7 +30724,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46197</v>
+        <v>46201</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
